--- a/etf_holdings/2026-08-25_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-25_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,55 +501,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>5.47%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>5.35%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>87518000</v>
+        <v>185000</v>
       </c>
       <c r="K2" t="n">
-        <v>89518000</v>
+        <v>186000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-24_00981A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -559,60 +559,60 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>294000</v>
+        <v>2289000</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3302000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-293,000</t>
+          <t>1,013,000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-24_00981A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,60 +622,60 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2000000</v>
+        <v>5285000</v>
       </c>
       <c r="K4" t="n">
-        <v>1957000</v>
+        <v>5315000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-43,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-08-24_00981A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -685,60 +685,60 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>200000</v>
+        <v>844000</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>849000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-199,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-08-24_00981A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -753,55 +753,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>142000</v>
+        <v>1800000</v>
       </c>
       <c r="K6" t="n">
-        <v>255000</v>
+        <v>1811000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>113,000</t>
+          <t>11,000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-24_00981A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,55 +816,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.66%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.45%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2395000</v>
+        <v>4386000</v>
       </c>
       <c r="K7" t="n">
-        <v>2407000</v>
+        <v>4412000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-24_00981A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -874,60 +874,60 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>410900</v>
+        <v>320000</v>
       </c>
       <c r="K8" t="n">
-        <v>383900</v>
+        <v>322000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-27,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-24_00981A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -942,55 +942,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1101000</v>
+        <v>901000</v>
       </c>
       <c r="K9" t="n">
-        <v>1301000</v>
+        <v>1486000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>585,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-24_00981A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1000,60 +1000,60 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>興勤</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>興勤</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.36%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.31%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1800000</v>
+        <v>2356000</v>
       </c>
       <c r="K10" t="n">
-        <v>1750000</v>
+        <v>2371000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50,000</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-24_00991A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1063,60 +1063,60 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.84%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.05%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1430000</v>
+        <v>1572000</v>
       </c>
       <c r="K11" t="n">
-        <v>1400000</v>
+        <v>1581000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-30,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-08-24_00991A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1126,60 +1126,60 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>鴻勁精密</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鴻勁精密</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>400000</v>
+        <v>1303000</v>
       </c>
       <c r="K12" t="n">
-        <v>380000</v>
+        <v>1311000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-20,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-24_00991A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1189,60 +1189,60 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6.48%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5.42%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>91000</v>
+        <v>4484000</v>
       </c>
       <c r="K13" t="n">
-        <v>80000</v>
+        <v>4511000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-11,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-24_00980A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1257,55 +1257,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>一詮</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>一詮</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>514000</v>
+        <v>950000</v>
       </c>
       <c r="K14" t="n">
-        <v>595000</v>
+        <v>1607000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>81,000</t>
+          <t>657,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-24_00980A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1320,55 +1320,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>台灣積體電路製造</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>台灣積體電路製造</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.87%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9.18%</t>
+          <t>2.97%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>663000</v>
+        <v>257000</v>
       </c>
       <c r="K15" t="n">
-        <v>753000</v>
+        <v>258000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>90,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-08-24_00980A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,55 +1383,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1942000</v>
+        <v>379000</v>
       </c>
       <c r="K16" t="n">
-        <v>2293000</v>
+        <v>381000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>351,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08-24_00980A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1441,60 +1441,60 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>聯發科技</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>聯發科技</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.93%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.77%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>254000</v>
+        <v>3396000</v>
       </c>
       <c r="K17" t="n">
-        <v>249000</v>
+        <v>3416000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-08-24_00980A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1509,48 +1509,48 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>187000</v>
+        <v>3432000</v>
       </c>
       <c r="K18" t="n">
-        <v>209000</v>
+        <v>3453000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-08-24_00980A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1562,37 +1562,55 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2486</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>一詮</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.49%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>0.88%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-0.49%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>3242000</v>
+      </c>
       <c r="K19" t="n">
-        <v>950000</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>2042000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-1,200,000</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>2026-08-24_00982A_full_holdings.xlsx</t>
@@ -1612,48 +1630,48 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>817000</v>
+        <v>3472000</v>
       </c>
       <c r="K20" t="n">
-        <v>727000</v>
+        <v>3494000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-90,000</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1675,48 +1693,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>碩天</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>碩天</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>4780000</v>
+        <v>603000</v>
       </c>
       <c r="K21" t="n">
-        <v>3242000</v>
+        <v>612000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-1,538,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1743,43 +1761,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>710000</v>
+        <v>959000</v>
       </c>
       <c r="K22" t="n">
-        <v>1910000</v>
+        <v>965000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1806,43 +1824,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>258000</v>
+        <v>1544000</v>
       </c>
       <c r="K23" t="n">
-        <v>774000</v>
+        <v>1563000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>516,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1869,43 +1887,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1440000</v>
+        <v>3533000</v>
       </c>
       <c r="K24" t="n">
-        <v>1650000</v>
+        <v>3552000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>210,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1917,7 +1935,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,55 +1950,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>5.95%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>5.96%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>20000</v>
+        <v>3828000</v>
       </c>
       <c r="K25" t="n">
-        <v>35000</v>
+        <v>3850000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-08-24_00403A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1990,60 +2008,60 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>700000</v>
+        <v>310000</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>312000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-699,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-08-24_00403A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2058,55 +2076,55 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>550000</v>
+        <v>321000</v>
       </c>
       <c r="K27" t="n">
-        <v>610000</v>
+        <v>322000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-08-24_00403A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2121,55 +2139,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>1680000</v>
+        <v>3504000</v>
       </c>
       <c r="K28" t="n">
-        <v>1800000</v>
+        <v>3524000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>120,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-08-24_00403A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2184,55 +2202,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>東元電機</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>東元電機</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>2856000</v>
+        <v>434000</v>
       </c>
       <c r="K29" t="n">
-        <v>3473000</v>
+        <v>437000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>617,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-08-24_00985A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,60 +2260,60 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>41000</v>
+        <v>774000</v>
       </c>
       <c r="K30" t="n">
-        <v>12000</v>
+        <v>1032000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-29,000</t>
+          <t>258,000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-08-24_00985A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2310,55 +2328,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>健策精密工業</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>健策精密工業</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>2.31%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>32000</v>
+        <v>1117000</v>
       </c>
       <c r="K31" t="n">
-        <v>49000</v>
+        <v>1123000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-08-24_00985A_full_holdings.xlsx</t>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2368,53 +2386,620 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>6672</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>騰輝電子-KY</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>騰輝電子-KY</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>546000</v>
+      </c>
+      <c r="K32" t="n">
+        <v>549000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8070</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>長華*</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>長華*</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>2871000</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2897000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>26,000</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-08-24_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1.12%</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="K34" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1,000,000</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-08-24_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>5.17%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>5.44%</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>+0.27%</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-08-24_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>1.49%</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0.66%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-0.83%</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>116000</v>
-      </c>
-      <c r="K32" t="n">
-        <v>56000</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>-60,000</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2026-08-24_00985A_full_holdings.xlsx</t>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>聯鈞</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>聯鈞</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0.13%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>-0.42%</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="K36" t="n">
+        <v>400000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-1,400,000</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-08-24_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3533</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>嘉澤</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>嘉澤</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>525000</v>
+      </c>
+      <c r="K37" t="n">
+        <v>300000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-225,000</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-08-24_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>譜瑞-KY</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>譜瑞-KY</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>500000</v>
+      </c>
+      <c r="K38" t="n">
+        <v>220000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-280,000</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-08-24_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2.32%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2.41%</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>610000</v>
+      </c>
+      <c r="K39" t="n">
+        <v>630000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-08-24_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.72%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0.86%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>700000</v>
+      </c>
+      <c r="K40" t="n">
+        <v>780000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-08-24_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1.10%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1720000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>120,000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-08-24_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
